--- a/output/Data and Chart Outputs/europe_biomethane_statistics.xlsx
+++ b/output/Data and Chart Outputs/europe_biomethane_statistics.xlsx
@@ -12,7 +12,8 @@
     <sheet name="Chart - Annual" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Monthly" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Annual" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Crosscheck" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Annual national" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Crosscheck" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -998,7 +999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A18"/>
+  <dimension ref="A1:A24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -1078,31 +1079,67 @@
     </row>
     <row r="13"/>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>Method</t>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Caveats and validation</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Incremental: DESNZ whole file is downloaded only when a new release URL appears (recorded below); AGGM re-fetched from two months before the last month saved; Eurostat refreshed in full.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16"/>
+          <t>Great Britain: the DESNZ monthly values are smooth (a constant daily rate per year, i.e. modelled/estimated from the quarterly and annual returns, note 6/7 on the sheet), not metered monthly data. National Gas's data portal carries biomethane for one NTS-connected plant only (Glentham), most GB biomethane enters distribution networks, so no operator daily series exists. DESNZ 2019 4.71 TWh vs Eurostat UK 4.89 TWh (gross vs net CV / revisions).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Austria: AGGM series SummeBioOesterreich exists from 2023; before that the East market area only (Tyrol and Vorarlberg entry series start 2023), so 2019-2022 are slightly understated. AGGM 2023 = 155 GWh vs Eurostat 121 GWh vs EBA Statistical Report 2024 (131 GWh injected by 14 plants). A zero/low month (Nov 2025) is a source gap, not a plant stop.</t>
+        </is>
+      </c>
+    </row>
     <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>Last pull</t>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>EBA Statistical Report (full country tables) is members-only; only a 17-page preview is public, so EBA is not tabulated here. GIE/EBA European Biomethane Map 2026 (PDF, no data download): installed capacity 8.2 bcm/year at end Q2 2026, 1,974 plants (86% grid-connected) - capacity, not injected volume. Eurostat EU27 was 33.2 TWh in 2023 and 37.1 TWh in 2024; Germany starts in 2021 (earlier years not reported, so the 2020-21 EU27 jump is a reporting break).</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-04 06:50 UTC</t>
+          <t>Italy: Eurostat annual only (3.2 TWh in 2024) - GSE blocks GitHub (HTTP 403) and Snam's portal is JavaScript-only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Method</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Incremental: DESNZ whole file is downloaded only when a new release URL appears (recorded below); AGGM re-fetched from two months before the last month saved; Eurostat refreshed in full.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>Last pull</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-10-04 06:52 UTC</t>
         </is>
       </c>
     </row>
@@ -5772,6 +5809,214 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>SE_upgraded_biogas_all_uses_TWh</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>SE_fed_into_gas_networks_TWh</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B2" t="n">
+        <v>0.112</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2006</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.218</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2007</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.303</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2008</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.355</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2009</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.488</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2010</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0.608</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0.734</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0.845</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B10" t="n">
+        <v>0.907</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B11" t="n">
+        <v>1.017</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B12" t="n">
+        <v>1.219</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B13" t="n">
+        <v>1.296</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B14" t="n">
+        <v>1.312</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B15" t="n">
+        <v>1.296</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B16" t="n">
+        <v>1.351</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B17" t="n">
+        <v>1.401</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B18" t="n">
+        <v>1.508</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B19" t="n">
+        <v>1.535</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B20" t="n">
+        <v>1.542</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.5347</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B21" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.547</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B22" t="n">
+        <v>1.805</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.531</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>

--- a/output/Data and Chart Outputs/europe_biomethane_statistics.xlsx
+++ b/output/Data and Chart Outputs/europe_biomethane_statistics.xlsx
@@ -161,6 +161,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Biomethane injected into the gas grid, monthly (national sources) (to Sep/26)</a:t>
             </a:r>
           </a:p>
@@ -337,6 +338,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Biomethane blended into / injected in the gas grid, annual by country (Eurostat; UK after 2019 DESNZ) (to 2025)</a:t>
             </a:r>
           </a:p>
@@ -526,7 +528,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="4A3AA7"/>
+              <a:srgbClr val="9A9A9A"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -1139,7 +1141,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-04 06:52 UTC</t>
+          <t>2026-10-28 00:51 UTC</t>
         </is>
       </c>
     </row>
@@ -2188,7 +2190,7 @@
         <v>46266</v>
       </c>
       <c r="C94" t="n">
-        <v>0.021114</v>
+        <v>0.021155</v>
       </c>
     </row>
   </sheetData>
@@ -2482,7 +2484,7 @@
         <v>0.4758</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2217000000000002</v>
+        <v>0.2217000000000011</v>
       </c>
       <c r="I9" t="n">
         <v>0.2306</v>
@@ -2522,7 +2524,7 @@
         <v>44197</v>
       </c>
       <c r="B11" t="n">
-        <v>4.93468</v>
+        <v>4.934679999999999</v>
       </c>
       <c r="C11" t="n">
         <v>10.1011</v>
@@ -2638,7 +2640,7 @@
         <v>45658</v>
       </c>
       <c r="B15" t="n">
-        <v>5.7603</v>
+        <v>5.760299999999999</v>
       </c>
     </row>
   </sheetData>
@@ -4164,7 +4166,7 @@
         <v>46266</v>
       </c>
       <c r="C154" t="n">
-        <v>21.114</v>
+        <v>21.155</v>
       </c>
     </row>
   </sheetData>
